--- a/laporan_padel_dki_jakarta_2026-09-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-15.xlsx
@@ -575,16 +575,16 @@
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.471.000</t>
+          <t>Rp4.468.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>56</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp1.204.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp8.350.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.574.500</t>
+          <t>Rp13.234.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.260.000</t>
+          <t>Rp3.680.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.088.000</t>
+          <t>Rp2.526.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.738.000</t>
+          <t>Rp2.314.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>75</v>
       </c>
       <c r="D31" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.072.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.610.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>48</v>
       </c>
       <c r="D39" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp780.000</t>
+          <t>Rp879.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.885.000</t>
+          <t>Rp1.790.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>176</v>
       </c>
       <c r="D42" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>84</v>
       </c>
       <c r="D46" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp3.205.000</t>
+          <t>Rp3.403.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>26</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp5.472.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>32</v>
       </c>
       <c r="D53" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>15</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp549.000</t>
+          <t>Rp898.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>42</v>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.930.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>56</v>
       </c>
       <c r="D59" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp599.000</t>
+          <t>Rp2.589.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>78</v>
       </c>
       <c r="D60" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp8.860.000</t>
+          <t>Rp9.060.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>80</v>
       </c>
       <c r="D65" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp4.328.000</t>
+          <t>Rp4.668.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>30</v>
       </c>
       <c r="D66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.720.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>96</v>
       </c>
       <c r="D69" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.937.500</t>
+          <t>Rp5.437.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>80</v>
       </c>
       <c r="D72" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.065.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>96</v>
       </c>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>84</v>
       </c>
       <c r="D77" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,21 +2838,21 @@
         <v>70</v>
       </c>
       <c r="D78" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2993,16 +2993,16 @@
         <v>84</v>
       </c>
       <c r="D83" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>26</v>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp594.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>32</v>
       </c>
       <c r="D90" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.309.000</t>
+          <t>Rp1.706.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>56</v>
       </c>
       <c r="D92" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp440.000</t>
+          <t>Rp880.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>105</v>
       </c>
       <c r="D93" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp2.510.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3394,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3447,16 +3447,16 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp729.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>84</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.250.000</t>
+          <t>Rp9.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp590.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>135</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.465.000</t>
+          <t>Rp7.515.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp10.250.000</t>
+          <t>Rp11.625.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.425.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>84</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.645.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4060,28 +4060,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Look Padel Kahfi I Jaksel</t>
+          <t>Club De Padel</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.580.000</t>
+          <t>Rp1.047.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rp165.000 - Rp195.000</t>
+          <t>Rp299.000 - Rp349.000</t>
         </is>
       </c>
     </row>
@@ -4091,28 +4091,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Padl Out</t>
+          <t>Look Padel Kahfi I Jaksel</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp120.000 - Rp350.000</t>
+          <t>Rp165.000 - Rp195.000</t>
         </is>
       </c>
     </row>
@@ -4122,28 +4122,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Field</t>
+          <t>Padl Out</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp2.000.000</t>
+          <t>Rp120.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -4153,28 +4153,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Padel Station By Vsports</t>
+          <t>The Field</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.155.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp10.000 - Rp385.000</t>
+          <t>Rp200.000 - Rp2.000.000</t>
         </is>
       </c>
     </row>
@@ -4184,28 +4184,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gilapadel Kebayoran Lama</t>
+          <t>Padel Station By Vsports</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp140.000</t>
+          <t>Rp10.000 - Rp385.000</t>
         </is>
       </c>
     </row>
@@ -4215,28 +4215,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Artepola</t>
+          <t>Gilapadel Kebayoran Lama</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp10.466.000</t>
+          <t>Rp240.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rp299.000 - Rp349.000</t>
+          <t>Rp80.000 - Rp140.000</t>
         </is>
       </c>
     </row>
@@ -4246,28 +4246,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HQ Padel &amp; Tennis</t>
+          <t>Artepola</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp15.995.000</t>
+          <t>Rp10.466.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp330.000</t>
+          <t>Rp299.000 - Rp349.000</t>
         </is>
       </c>
     </row>
@@ -4277,28 +4277,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Estate Padel Club - Kemang</t>
+          <t>HQ Padel &amp; Tennis</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp15.995.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp325.000</t>
+          <t>Rp175.000 - Rp330.000</t>
         </is>
       </c>
     </row>
@@ -4308,28 +4308,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ribens Padel Fatmawati</t>
+          <t>The Estate Padel Club - Kemang</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp300.000</t>
+          <t>Rp250.000 - Rp325.000</t>
         </is>
       </c>
     </row>
@@ -4339,28 +4339,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Court Cirendeu</t>
+          <t>Ribens Padel Fatmawati</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.299.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp200.000</t>
+          <t>Rp200.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -4370,28 +4370,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Padel Bros</t>
+          <t>The Court Cirendeu</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.299.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp375.000</t>
+          <t>Rp50.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -4401,28 +4401,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Padel Mezcal</t>
+          <t>Padel Bros</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D33" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp200.000 - Rp375.000</t>
         </is>
       </c>
     </row>
@@ -4432,28 +4432,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>K30 Padel</t>
+          <t>Padel Mezcal</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4463,28 +4463,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Padelplay</t>
+          <t>K30 Padel</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp250.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4494,28 +4494,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>La Corte de Padel</t>
+          <t>Padelplay</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp567.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp169.000 - Rp189.000</t>
+          <t>Rp160.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4525,28 +4525,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Racket Kuningan</t>
+          <t>La Corte de Padel</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="D37" t="n">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp16.500.000</t>
+          <t>Rp567.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp600.000</t>
+          <t>Rp169.000 - Rp189.000</t>
         </is>
       </c>
     </row>
@@ -4556,28 +4556,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Padel Court 57 Kemang</t>
+          <t>Racket Kuningan</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp18.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp350.000</t>
+          <t>Rp150.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -4587,28 +4587,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Second Serve Padel</t>
+          <t>Padel Court 57 Kemang</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp375.000</t>
+          <t>Rp250.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -4618,28 +4618,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Rooftop Kyzn Kuningan</t>
+          <t>Second Serve Padel</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp1.000.000</t>
+          <t>Rp275.000 - Rp375.000</t>
         </is>
       </c>
     </row>
@@ -4649,28 +4649,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Space Padel ITC Fatmawati</t>
+          <t>The Rooftop Kyzn Kuningan</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp300.000 - Rp1.000.000</t>
         </is>
       </c>
     </row>
@@ -4680,28 +4680,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Victoria Social Club - Kemang</t>
+          <t>Space Padel ITC Fatmawati</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp499.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -4711,28 +4711,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boenny Padel Society</t>
+          <t>Victoria Social Club - Kemang</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp300.000</t>
+          <t>Rp300.000 - Rp499.000</t>
         </is>
       </c>
     </row>
@@ -4742,18 +4742,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TOM'S PADEL by Sira</t>
+          <t>Boenny Padel Society</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>52</v>
       </c>
       <c r="D44" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp175.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -4773,28 +4773,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MMS ARENA</t>
+          <t>TOM'S PADEL by Sira</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp1.100.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4804,28 +4804,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BM Padel Jagakarsa</t>
+          <t>MMS ARENA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp9.300.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp250.000 - Rp1.100.000</t>
         </is>
       </c>
     </row>
@@ -4835,28 +4835,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Serve and Rally Reserve</t>
+          <t>BM Padel Jagakarsa</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp350.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4866,28 +4866,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fourthwall</t>
+          <t>Serve and Rally Reserve</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp300.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -4897,28 +4897,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Binakarsa Green Courts</t>
+          <t>Fourthwall</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.734.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp332.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
     </row>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Desimal Padel</t>
+          <t>Binakarsa Green Courts</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D50" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.875.000</t>
+          <t>Rp4.734.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp250.000</t>
+          <t>Rp250.000 - Rp332.000</t>
         </is>
       </c>
     </row>
@@ -4959,28 +4959,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AIR Padel Active</t>
+          <t>Desimal Padel</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp225.000</t>
+          <t>Rp125.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -4990,28 +4990,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GOAT Arena Cibis</t>
+          <t>AIR Padel Active</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D52" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.340.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp396.000</t>
+          <t>Rp125.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -5021,28 +5021,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Padel Parc MT Haryono By DOOgether</t>
+          <t>GOAT Arena Cibis</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp7.250.000</t>
+          <t>Rp9.132.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp400.000</t>
+          <t>Rp300.000 - Rp396.000</t>
         </is>
       </c>
     </row>
@@ -5052,28 +5052,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clubhouse Gandaria</t>
+          <t>Padel Parc MT Haryono By DOOgether</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D54" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp7.250.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp350.000</t>
+          <t>Rp250.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -5083,28 +5083,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>All Play Kemang | Padel &amp; Pickle</t>
+          <t>Clubhouse Gandaria</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp360.000</t>
+          <t>Rp250.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -5114,28 +5114,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Trilogi Arena By Duale</t>
+          <t>All Play Kemang | Padel &amp; Pickle</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>60</v>
       </c>
       <c r="D56" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp4.415.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp330.000</t>
+          <t>Rp200.000 - Rp360.000</t>
         </is>
       </c>
     </row>
@@ -5145,28 +5145,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lifestyle Capital Club (LCC): Padel Court, Padel/Tennis/Golf Simulator, Cafe &amp; Working Space</t>
+          <t>Trilogi Arena By Duale</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D57" t="n">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp4.710.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp500.000</t>
+          <t>Rp275.000 - Rp330.000</t>
         </is>
       </c>
     </row>
@@ -5176,28 +5176,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Padel un Terra Simulator</t>
+          <t>Lifestyle Capital Club (LCC): Padel Court, Padel/Tennis/Golf Simulator, Cafe &amp; Working Space</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D58" t="n">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp399.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rp53.000 - Rp71.000</t>
+          <t>Rp150.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -5207,28 +5207,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Padel Venue</t>
+          <t>Padel un Terra Simulator</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp399.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp175.000</t>
+          <t>Rp53.000 - Rp71.000</t>
         </is>
       </c>
     </row>
@@ -5238,28 +5238,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4-Play Padel Simulator</t>
+          <t>Padel Venue</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="D60" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp175.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp120.000</t>
+          <t>Rp150.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -5269,28 +5269,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Round Padel</t>
+          <t>4-Play Padel Simulator</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.215.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rp235.000 - Rp275.000</t>
+          <t>Rp100.000 - Rp120.000</t>
         </is>
       </c>
     </row>
@@ -5300,28 +5300,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dome Padel, Tebet</t>
+          <t>Round Padel</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp1.215.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp350.000 - Rp400.000</t>
+          <t>Rp235.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -5331,28 +5331,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jungle Padel Jakarta</t>
+          <t>Oasis Padel Kuningan</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D63" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp300.000 - Rp475.000</t>
         </is>
       </c>
     </row>
@@ -5362,28 +5362,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Grand Sports Padel</t>
+          <t>Dome Padel, Tebet</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp7.600.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp400.000</t>
+          <t>Rp350.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5393,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fork Padel</t>
+          <t>Jungle Padel Jakarta</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D65" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp350.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
     </row>
@@ -5424,28 +5424,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T3 Sports &amp; Lifestyle</t>
+          <t>Grand Sports Padel</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="D66" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp20.850.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp600.000</t>
+          <t>Rp250.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -5455,28 +5455,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mpadl</t>
+          <t>Padel Parc Arkadia</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D67" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp3.267.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp180.000 - Rp297.000</t>
         </is>
       </c>
     </row>
@@ -5486,26 +5486,119 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>Fork Padel</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>60</v>
+      </c>
+      <c r="D68" t="n">
+        <v>45</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rp5.250.000</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Rp180.000 - Rp350.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>T3 Sports &amp; Lifestyle</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>117</v>
+      </c>
+      <c r="D69" t="n">
+        <v>80</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rp18.750.000</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Rp150.000 - Rp600.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Mpadl</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>30</v>
+      </c>
+      <c r="D70" t="n">
+        <v>13</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>56.7%</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rp2.350.000</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Rp125.000 - Rp150.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>PPPLATZ</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="C71" t="n">
         <v>26</v>
       </c>
-      <c r="D68" t="n">
-        <v>12</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Rp2.800.000</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="D71" t="n">
+        <v>11</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rp3.000.000</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>Rp200.000</t>
         </is>
@@ -5637,16 +5730,16 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5758,19 +5851,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp31.950.000</t>
+          <t>Rp32.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5792,16 +5885,16 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5823,16 +5916,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.020.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5885,16 +5978,16 @@
         <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.510.000</t>
+          <t>Rp9.180.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5956,7 +6049,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6009,16 +6102,16 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6040,16 +6133,16 @@
         <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6102,16 +6195,16 @@
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp684.000</t>
+          <t>Rp1.020.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6133,16 +6226,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp6.790.000</t>
+          <t>Rp8.990.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6246,16 +6339,16 @@
         <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp5.270.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6339,16 +6432,16 @@
         <v>180</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp12.850.000</t>
+          <t>Rp13.240.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6370,16 +6463,16 @@
         <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6401,16 +6494,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6432,16 +6525,16 @@
         <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.825.000</t>
+          <t>Rp7.143.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6463,16 +6556,16 @@
         <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6494,16 +6587,16 @@
         <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp13.010.500</t>
+          <t>Rp14.130.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6587,16 +6680,16 @@
         <v>120</v>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.060.000</t>
+          <t>Rp5.420.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6649,16 +6742,16 @@
         <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6742,16 +6835,16 @@
         <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.259.000</t>
+          <t>Rp2.797.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6804,16 +6897,16 @@
         <v>126</v>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.500.000</t>
+          <t>Rp22.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6844,7 +6937,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6866,16 +6959,16 @@
         <v>98</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.380.000</t>
+          <t>Rp6.443.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6897,16 +6990,16 @@
         <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6959,16 +7052,16 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp475.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6990,16 +7083,16 @@
         <v>84</v>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7021,16 +7114,16 @@
         <v>56</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.990.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7052,16 +7145,16 @@
         <v>56</v>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.470.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7083,16 +7176,16 @@
         <v>70</v>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7145,16 +7238,16 @@
         <v>90</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.295.000</t>
+          <t>Rp9.540.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7176,16 +7269,16 @@
         <v>165</v>
       </c>
       <c r="D33" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp20.300.000</t>
+          <t>Rp22.025.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7238,16 +7331,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.565.000</t>
+          <t>Rp3.990.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7269,16 +7362,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7300,16 +7393,16 @@
         <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.232.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7362,16 +7455,16 @@
         <v>125</v>
       </c>
       <c r="D39" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp21.575.000</t>
+          <t>Rp22.425.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7393,16 +7486,16 @@
         <v>112</v>
       </c>
       <c r="D40" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7424,16 +7517,16 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7548,16 +7641,16 @@
         <v>30</v>
       </c>
       <c r="D45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp5.430.000</t>
+          <t>Rp5.930.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7579,16 +7672,16 @@
         <v>90</v>
       </c>
       <c r="D46" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7641,16 +7734,16 @@
         <v>120</v>
       </c>
       <c r="D48" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp3.810.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7754,16 +7847,16 @@
         <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7785,16 +7878,16 @@
         <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.770.000</t>
+          <t>Rp9.230.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7816,16 +7909,16 @@
         <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7909,16 +8002,16 @@
         <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.315.000</t>
+          <t>Rp2.465.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -7940,16 +8033,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp2.195.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7971,16 +8064,16 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8002,16 +8095,16 @@
         <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.730.000</t>
+          <t>Rp6.240.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8033,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.340.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8095,16 +8188,16 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8126,16 +8219,16 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8157,16 +8250,16 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8250,16 +8343,16 @@
         <v>45</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.055.000</t>
+          <t>Rp2.305.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8343,16 +8436,16 @@
         <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.080.000</t>
+          <t>Rp18.480.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8436,16 +8529,16 @@
         <v>120</v>
       </c>
       <c r="D24" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.395.000</t>
+          <t>Rp7.575.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8529,16 +8622,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.095.000</t>
+          <t>Rp3.310.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8560,16 +8653,16 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp705.000</t>
+          <t>Rp995.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8591,16 +8684,16 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8653,16 +8746,16 @@
         <v>45</v>
       </c>
       <c r="D31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8808,16 +8901,16 @@
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.880.000</t>
+          <t>Rp6.080.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8839,16 +8932,16 @@
         <v>42</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8870,16 +8963,16 @@
         <v>60</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.388.000</t>
+          <t>Rp1.586.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8932,16 +9025,16 @@
         <v>52</v>
       </c>
       <c r="D40" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp338.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -8994,16 +9087,16 @@
         <v>56</v>
       </c>
       <c r="D42" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.383.000</t>
+          <t>Rp2.587.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-15.xlsx
@@ -482,16 +482,16 @@
         <v>96</v>
       </c>
       <c r="D2" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.360.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>128</v>
       </c>
       <c r="D4" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.380.000</t>
+          <t>Rp12.580.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.468.000</t>
+          <t>Rp5.463.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>56</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.204.000</t>
+          <t>Rp1.580.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.489.990</t>
+          <t>Rp4.187.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.234.500</t>
+          <t>Rp12.427.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>128</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.485.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>50</v>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.314.000</t>
+          <t>Rp2.602.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.710.000</t>
+          <t>Rp4.940.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>64</v>
       </c>
       <c r="D33" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.008.000</t>
+          <t>Rp4.204.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>64</v>
       </c>
       <c r="D35" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.610.000</t>
+          <t>Rp4.170.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>48</v>
       </c>
       <c r="D39" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp879.000</t>
+          <t>Rp1.074.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>56</v>
       </c>
       <c r="D43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.472.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp120.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>15</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp898.000</t>
+          <t>Rp1.098.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>78</v>
       </c>
       <c r="D60" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp9.060.000</t>
+          <t>Rp9.160.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>30</v>
       </c>
       <c r="D67" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>160</v>
       </c>
       <c r="D68" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp3.885.000</t>
+          <t>Rp2.889.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>96</v>
       </c>
       <c r="D69" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.437.500</t>
+          <t>Rp5.687.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>64</v>
       </c>
       <c r="D71" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.995.000</t>
+          <t>Rp2.335.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>84</v>
       </c>
       <c r="D77" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>70</v>
       </c>
       <c r="D78" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>117</v>
       </c>
       <c r="D82" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>84</v>
       </c>
       <c r="D83" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>112</v>
       </c>
       <c r="D86" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>98</v>
       </c>
       <c r="D88" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.120.000</t>
+          <t>Rp3.480.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>56</v>
       </c>
       <c r="D92" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>105</v>
       </c>
       <c r="D93" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp465.000</t>
+          <t>Rp590.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>84</v>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.850.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp2.360.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>52</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp10.466.000</t>
+          <t>Rp11.164.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.299.000</t>
+          <t>Rp1.499.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>26</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>75</v>
       </c>
       <c r="D34" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>65</v>
       </c>
       <c r="D36" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>52</v>
       </c>
       <c r="D55" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>75</v>
       </c>
       <c r="D66" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp8.800.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>60</v>
       </c>
       <c r="D68" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5668,16 +5668,16 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp680.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>84</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D8" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5863,12 +5863,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp32.200.000</t>
+          <t>Rp33.050.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp800.000</t>
+          <t>Rp180.000 - Rp800.000</t>
         </is>
       </c>
     </row>
@@ -5885,16 +5885,16 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.880.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.410.000</t>
+          <t>Rp4.695.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6308,16 +6308,16 @@
         <v>174</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp8.190.000</t>
+          <t>Rp8.110.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.270.000</t>
+          <t>Rp4.910.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp168.000</t>
+          <t>Rp574.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>180</v>
       </c>
       <c r="D6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.240.000</t>
+          <t>Rp13.435.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.143.000</t>
+          <t>Rp7.615.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.460.000</t>
+          <t>Rp5.058.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>120</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.420.000</t>
+          <t>Rp5.880.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>84</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.531.000</t>
+          <t>Rp5.506.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>126</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.400.000</t>
+          <t>Rp22.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>98</v>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.443.000</t>
+          <t>Rp5.845.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>90</v>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.968.000</t>
+          <t>Rp5.243.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>70</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>90</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp9.540.000</t>
+          <t>Rp9.785.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>165</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp22.025.000</t>
+          <t>Rp23.900.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>56</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.628.000</t>
+          <t>Rp2.204.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp23.400.000</t>
+          <t>Rp25.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>84</v>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>30</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp5.930.000</t>
+          <t>Rp6.330.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>120</v>
       </c>
       <c r="D48" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp4.290.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>48</v>
       </c>
       <c r="D49" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>39</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.465.000</t>
+          <t>Rp3.015.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp6.790.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.319.500</t>
+          <t>Rp8.779.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp270.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.196.000</t>
+          <t>Rp2.896.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.480.000</t>
+          <t>Rp18.960.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>60</v>
       </c>
       <c r="D23" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.745.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.535.000</t>
+          <t>Rp1.734.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.140.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>45</v>
       </c>
       <c r="D32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.947.000</t>
+          <t>Rp4.292.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>42</v>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.560.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>60</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.586.000</t>
+          <t>Rp1.883.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>60</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-15.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-15.xlsx
@@ -544,16 +544,16 @@
         <v>128</v>
       </c>
       <c r="D4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.580.000</t>
+          <t>Rp12.830.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.187.988</t>
+          <t>Rp4.483.988</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.427.500</t>
+          <t>Rp12.505.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.780.000</t>
+          <t>Rp4.905.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>64</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.170.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>45</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.790.000</t>
+          <t>Rp1.960.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp198.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>60</v>
       </c>
       <c r="D61" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.390.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>64</v>
       </c>
       <c r="D71" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.335.000</t>
+          <t>Rp2.485.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>70</v>
       </c>
       <c r="D78" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>32</v>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.703.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>32</v>
       </c>
       <c r="D84" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>112</v>
       </c>
       <c r="D86" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp8.450.000</t>
+          <t>Rp8.325.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>30</v>
       </c>
       <c r="D91" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.175.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.975.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>84</v>
       </c>
       <c r="D17" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.360.000</t>
+          <t>Rp3.460.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>140</v>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp15.995.000</t>
+          <t>Rp16.520.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>26</v>
       </c>
       <c r="D41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>45</v>
       </c>
       <c r="D54" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.250.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>84</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.074.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.675.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp574.000</t>
+          <t>Rp949.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>180</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.435.000</t>
+          <t>Rp13.825.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>126</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.800.000</t>
+          <t>Rp23.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>90</v>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.243.000</t>
+          <t>Rp5.442.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>165</v>
       </c>
       <c r="D33" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp23.900.000</t>
+          <t>Rp24.300.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.990.000</t>
+          <t>Rp4.189.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>125</v>
       </c>
       <c r="D39" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp22.425.000</t>
+          <t>Rp22.875.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>30</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp6.330.000</t>
+          <t>Rp6.730.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.195.000</t>
+          <t>Rp2.495.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.240.000</t>
+          <t>Rp6.540.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.734.000</t>
+          <t>Rp2.034.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
